--- a/converted/Edited HTML Form_converted.xlsx
+++ b/converted/Edited HTML Form_converted.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,17 +477,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pregnancy / Breastfeeding status:</t>
+          <t>Previously tested HIV negative</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -497,12 +497,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pregnancyBreastfeedingStatus_4</t>
+          <t>previouslyTestedHivNegative_4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -518,22 +518,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Last menstrual period:</t>
+          <t>Ever had sexual intercourse</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -543,13 +543,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>lastMenstrualPeriod_5</t>
+          <t>everHadSexualIntercourse_5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -559,22 +559,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gestational age in weeks:</t>
+          <t>Client Pregnant (Test and ensure linkage to PMTCT Program)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -584,13 +584,13 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>gestationalAgeInWeeks_6</t>
+          <t>clientPregnantTestAndEnsureLinkageToPmtctProgram_6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -600,22 +600,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Expected date of delivery:</t>
+          <t>Blood transfusion in last 3 months</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -625,13 +625,13 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>expectedDateOfDelivery_7</t>
+          <t>bloodTransfusionInLast3Months_7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -641,17 +641,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Did child receive prophylaxis?</t>
+          <t>Client informed about HIV transmission routes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>didChildReceiveProphylaxis_8</t>
+          <t>clientInformedAboutHivTransmissionRoutes_8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -682,71 +682,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Weight (kg)</t>
+          <t>Unprotected sex with casual partner in last 3 months</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>weightKg_9</t>
+          <t>unprotectedSexWithCasualPartnerInLast3Months_9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Height (cm)</t>
+          <t>Client informed about risk factors for HIV transmission</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -756,46 +748,38 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>heightCm_10</t>
+          <t>clientInformedAboutRiskFactorsForHivTransmission_10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>272.0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Length (cm)</t>
+          <t>Unprotected sex with regular partner in the last 3 months</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -805,46 +789,38 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>lengthCm_11</t>
+          <t>unprotectedSexWithRegularPartnerInTheLast3Months_11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>272.0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Temp (c)</t>
+          <t>Client informed on preventing HIV transmission methods</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -854,46 +830,38 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>tempC_12</t>
+          <t>clientInformedOnPreventingHivTransmissionMethods_12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SYSTOLIC</t>
+          <t>STI in last 3 months</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -903,46 +871,38 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>systolic_13</t>
+          <t>stiInLast3Months_13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>Client informed about possible test results</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -952,46 +912,38 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>q_14</t>
+          <t>clientInformedAboutPossibleTestResults_14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Body Mass Index (BMI)</t>
+          <t>More than 1 sex partner during last 3 months</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1001,41 +953,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>bodyMassIndexBmi_15</t>
+          <t>moreThan1SexPartnerDuringLast3Months_15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MUAC Interpretation</t>
+          <t>Informed consent for HIV testing given</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1050,7 +994,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>muacInterpretation_16</t>
+          <t>informedConsentForHivTestingGiven_16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1066,17 +1010,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MUAC</t>
+          <t>Risk Assesment Score</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1091,7 +1035,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>muac_17</t>
+          <t>riskAssesmentScore_17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1107,38 +1051,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Is Patient on Family Planning</t>
+          <t>Current Cough</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>isPatientOnFamilyPlanning_18</t>
+          <t>currentCough_18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1148,17 +1092,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Family planning Method:</t>
+          <t>Complaints of vaginal discharge or burning when urinating?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1173,7 +1117,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>familyPlanningMethod_19</t>
+          <t>complaintsOfVaginalDischargeOrBurningWhenUrinating_19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1189,17 +1133,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pregnancy/Breastfeeding Status</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pregnancy / Breastfeeding status:</t>
+          <t>Weight Loss</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1214,7 +1158,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pregnancyBreastfeedingStatus_20</t>
+          <t>weightLoss_20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1230,22 +1174,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pregnancy/Breastfeeding Status</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Last menstrual period:</t>
+          <t>Complaints of lower abdominal pains with or without vaginal discharge?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1255,13 +1199,13 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>lastMenstrualPeriod_21</t>
+          <t>complaintsOfLowerAbdominalPainsWithOrWithoutVaginalDischarge_21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1271,38 +1215,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pregnancy/Breastfeeding Status</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gestational age in weeks:</t>
+          <t>Fever</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>gestationalAgeInWeeks_22</t>
+          <t>fever_22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1312,22 +1256,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pregnancy/Breastfeeding Status</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Expected date of delivery:</t>
+          <t>Complaints of urethral discharge or burning when urinating?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1337,13 +1281,13 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>expectedDateOfDelivery_23</t>
+          <t>complaintsOfUrethralDischargeOrBurningWhenUrinating_23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1353,17 +1297,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pregnancy/Breastfeeding Status</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Did child receive prophylaxis?</t>
+          <t>Night sweats</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1373,12 +1317,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>didChildReceiveProphylaxis_24</t>
+          <t>nightSweats_24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1394,17 +1338,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Functional Status</t>
+          <t>Complaints of scrotal swelling and pain</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1419,7 +1363,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>functionalStatus_25</t>
+          <t>complaintsOfScrotalSwellingAndPain_25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1435,17 +1379,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WHO Clinical stage</t>
+          <t>Contact with TB+ patient</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1460,7 +1404,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>whoClinicalStage_26</t>
+          <t>contactWithTbPatient_26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1476,17 +1420,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TB Status</t>
+          <t>Complaints of genital sore(s) or swollen inguinal lymph nodes with or without pains?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1496,12 +1440,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>tbStatus_27</t>
+          <t>complaintsOfGenitalSoresOrSwollenInguinalLymphNodesWithOrWithoutPains_27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1517,22 +1461,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clinical Information</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Method of Diagnosis</t>
+          <t>TB Screening Score</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Numeric</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1542,13 +1486,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>methodOfDiagnosis_28</t>
+          <t>tbScreeningScore_28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1558,22 +1502,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cryptococcal Screening Status</t>
+          <t>Pre-Test Information</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cryptococcal Screening status</t>
+          <t>STI Screening Score</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Numeric</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1583,13 +1527,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>cryptococcalScreeningStatus_29</t>
+          <t>stiScreeningScore_29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1599,17 +1543,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cryptococcal Screening Status</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cervical Cancer Screening Status</t>
+          <t>Test result</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1624,7 +1568,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>cervicalCancerScreeningStatus_30</t>
+          <t>testResult_30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1640,22 +1584,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cryptococcal Screening Status</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Specify:</t>
+          <t>HIV Confirmatory Test</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1665,13 +1609,13 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>specify_31</t>
+          <t>hivConfirmatoryTest_31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1681,17 +1625,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cryptococcal Screening Status</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Treatment Provided</t>
+          <t>Tie Breaker</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1706,7 +1650,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>treatmentProvided_32</t>
+          <t>tieBreaker_32</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1722,22 +1666,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>Test date</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1747,13 +1691,13 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>icpcHivAndOpportunisticInfectionDiagnoses_33</t>
+          <t>testDate_33</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1763,22 +1707,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses (2)</t>
+          <t>HIV Confirmatory Test Date</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1788,13 +1732,13 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>icpcHivAndOpportunisticInfectionDiagnoses2_34</t>
+          <t>hivConfirmatoryTestDate_34</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1804,22 +1748,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses (3)</t>
+          <t>Tie Breaker Date</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1829,13 +1773,13 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>icpcHivAndOpportunisticInfectionDiagnoses3_35</t>
+          <t>tieBreakerDate_35</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1845,17 +1789,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Test Results</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses (4)</t>
+          <t>Final Result</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1870,7 +1814,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>icpcHivAndOpportunisticInfectionDiagnoses4_36</t>
+          <t>finalResult_36</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1886,17 +1830,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other Symptom</t>
+          <t>Opt Out of RTRI?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1911,7 +1855,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>otherSymptom_37</t>
+          <t>optOutOfRtri_37</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1927,17 +1871,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>antiretroviral drug side effects, since last visit</t>
+          <t>Test name</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1952,7 +1896,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>antiretroviralDrugSideEffectsSinceLastVisit_38</t>
+          <t>testName_38</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1968,22 +1912,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>antiretroviral drug side effects, since last visit (2)</t>
+          <t>Test date</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1993,13 +1937,13 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>antiretroviralDrugSideEffectsSinceLastVisit2_39</t>
+          <t>testDate_39</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2009,22 +1953,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>antiretroviral drug side effects, since last visit (3)</t>
+          <t>HIV Recency Test Name</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2034,13 +1978,13 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>antiretroviralDrugSideEffectsSinceLastVisit3_40</t>
+          <t>hivRecencyTestName_40</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2050,22 +1994,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>antiretroviral drug side effects, since last visit (4)</t>
+          <t>Verify Participant ID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2075,13 +2019,13 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>antiretroviralDrugSideEffectsSinceLastVisit4_41</t>
+          <t>verifyParticipantId_41</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2091,17 +2035,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>antiretroviral drug side effects, since last visit (5)</t>
+          <t>Control Line</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2116,7 +2060,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>antiretroviralDrugSideEffectsSinceLastVisit5_42</t>
+          <t>controlLine_42</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2132,17 +2076,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>antiretroviral drug side effects, since last visit (6)</t>
+          <t>Verification Line</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2157,7 +2101,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>antiretroviralDrugSideEffectsSinceLastVisit6_43</t>
+          <t>verificationLine_43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2173,22 +2117,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nausea and Vomiting
-                                Headache
-                                Insomnia
-                                Weakness
-                                PV Bleeding / Discharge
-                                Fat changes</t>
+          <t>Long-Term Line</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2203,7 +2142,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>nauseaAndVomitingHeadacheInsomniaWeaknessPvBleedingDischargeFatChanges_44</t>
+          <t>longtermLine_44</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2219,22 +2158,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nausea and Vomiting
-                                Headache
-                                Insomnia
-                                Weakness
-                                PV Bleeding / Discharge
-                                Fat changes (2)</t>
+          <t>Recency Interpretation</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2249,7 +2183,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>nauseaAndVomitingHeadacheInsomniaWeaknessPvBleedingDischargeFatChanges2_45</t>
+          <t>recencyInterpretation_45</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2265,22 +2199,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nausea and Vomiting
-                                Headache
-                                Insomnia
-                                Weakness
-                                PV Bleeding / Discharge
-                                Fat changes (3)</t>
+          <t>Viral load request</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2295,7 +2224,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>nauseaAndVomitingHeadacheInsomniaWeaknessPvBleedingDischargeFatChanges3_46</t>
+          <t>viralLoadRequest_46</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2311,27 +2240,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nausea and Vomiting
-                                Headache
-                                Insomnia
-                                Weakness
-                                PV Bleeding / Discharge
-                                Fat changes (4)</t>
+          <t>Sample collection date</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2341,13 +2265,13 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>nauseaAndVomitingHeadacheInsomniaWeaknessPvBleedingDischargeFatChanges4_47</t>
+          <t>sampleCollectionDate_47</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2357,27 +2281,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nausea and Vomiting
-                                Headache
-                                Insomnia
-                                Weakness
-                                PV Bleeding / Discharge
-                                Fat changes (5)</t>
+          <t>Sample Reference Number:</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2387,13 +2306,13 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>nauseaAndVomitingHeadacheInsomniaWeaknessPvBleedingDischargeFatChanges5_48</t>
+          <t>sampleReferenceNumber_48</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2403,27 +2322,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ICPC HIV and opportunistic infection diagnoses</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nausea and Vomiting
-                                Headache
-                                Insomnia
-                                Weakness
-                                PV Bleeding / Discharge
-                                Fat changes (6)</t>
+          <t>Sample Type</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2433,13 +2347,13 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>nauseaAndVomitingHeadacheInsomniaWeaknessPvBleedingDischargeFatChanges6_49</t>
+          <t>sampleType_49</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2449,38 +2363,38 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DSD Status</t>
+          <t>Date Sample Sent to PCR Lab</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>dsdStatus_50</t>
+          <t>dateSampleSentToPcrLab_50</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2490,22 +2404,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dispensing Modality</t>
+          <t>Date sample received at PCR Lab</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2515,13 +2429,13 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>dispensingModality_51</t>
+          <t>dateSampleReceivedAtPcrLab_51</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2531,22 +2445,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Facility Dispensing</t>
+          <t>Date result was sent from PCR Lab</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2556,13 +2470,13 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>facilityDispensing_52</t>
+          <t>dateResultWasSentFromPcrLab_52</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2572,17 +2486,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DSD Start Date</t>
+          <t>Date Sample Ordered</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2597,7 +2511,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>dsdStartDate_53</t>
+          <t>dateSampleOrdered_53</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2613,22 +2527,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Community Dispensing</t>
+          <t>Date result was received at the facility</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2638,13 +2552,13 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>communityDispensing_54</t>
+          <t>dateResultWasReceivedAtTheFacility_54</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2654,22 +2568,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DSD Model</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DSD Start Date (2)</t>
+          <t>Receiving PCR Lab</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2679,13 +2593,13 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>dsdStartDate2_55</t>
+          <t>receivingPcrLab_55</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2695,17 +2609,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ARV Medication Plan</t>
+          <t>Viral Load Result Classification:</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2720,7 +2634,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>arvMedicationPlan_56</t>
+          <t>viralLoadResultClassification_56</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2736,22 +2650,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Regimen substitution reason</t>
+          <t>Result (copies/ml)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Numeric</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2761,33 +2675,37 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>regimenSubstitutionReason_57</t>
+          <t>resultCopiesml_57</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Regimen switch reasons</t>
+          <t>Final Recency Result:</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2802,7 +2720,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>regimenSwitchReasons_58</t>
+          <t>finalRecencyResult_58</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -2818,22 +2736,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Regimen stop reasons</t>
+          <t>Assay Date</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2843,13 +2761,13 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>regimenStopReasons_59</t>
+          <t>assayDate_59</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2859,17 +2777,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medication Plan</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Date Stopped Regimen</t>
+          <t>Approval Date</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2884,7 +2802,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>dateStoppedRegimen_60</t>
+          <t>approvalDate_60</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2900,22 +2818,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Current Regimen Line</t>
+          <t>Result Date</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2925,13 +2843,13 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>currentRegimenLine_61</t>
+          <t>resultDate_61</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -2941,22 +2859,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>HIV Recency Testing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Adult 1st line ARV regimen</t>
+          <t>Sample test date</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2966,13 +2884,13 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>adult1stLineArvRegimen_62</t>
+          <t>sampleTestDate_62</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -2982,17 +2900,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Adult 2nd line ARV regimen</t>
+          <t>Have you been tested for HIV before within this year</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3007,7 +2925,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>adult2ndLineArvRegimen_63</t>
+          <t>haveYouBeenTestedForHivBeforeWithinThisYear_63</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3023,17 +2941,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Adult 3rd Line ARV Regimens</t>
+          <t>Risk reduction plan developed</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3048,7 +2966,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>adult3rdLineArvRegimens_64</t>
+          <t>riskReductionPlanDeveloped_64</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3064,17 +2982,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Child 1st line ARV regimen</t>
+          <t>HIV Request and Result form signed by tester(s)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3089,7 +3007,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>child1stLineArvRegimen_65</t>
+          <t>hivRequestAndResultFormSignedByTesters_65</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3105,17 +3023,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Child 2nd line ARV regimen</t>
+          <t>Post test disclosure plan developed</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3130,7 +3048,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>child2ndLineArvRegimen_66</t>
+          <t>postTestDisclosurePlanDeveloped_66</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -3146,17 +3064,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Child 3rd Line ARV Regimens</t>
+          <t>HIV Request and Result form filled with CT Intake Form</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3171,7 +3089,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>child3rdLineArvRegimens_67</t>
+          <t>hivRequestAndResultFormFilledWithCtIntakeForm_67</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3187,17 +3105,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ARV Drugs Adherence</t>
+          <t>Will bring partner(s) for HIV testing</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3212,7 +3130,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>arvDrugsAdherence_68</t>
+          <t>willBringPartnersForHivTesting_68</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3228,17 +3146,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poor ARV Adherence Reason</t>
+          <t>Client received HIV test result</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3253,7 +3171,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>poorArvAdherenceReason_69</t>
+          <t>clientReceivedHivTestResult_69</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3269,17 +3187,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poor ARV Adherence Reason (2)</t>
+          <t>Will bring own children less than 5 years for HIV testing</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3294,7 +3212,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>poorArvAdherenceReason2_70</t>
+          <t>willBringOwnChildrenLessThan5YearsForHivTesting_70</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3310,17 +3228,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cotrimoxazole Dose</t>
+          <t>Post test counseling done</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3335,7 +3253,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>cotrimoxazoleDose_71</t>
+          <t>postTestCounselingDone_71</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3351,17 +3269,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Septra adherence</t>
+          <t>Provided with information on FP and dual contraception</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3376,7 +3294,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>septraAdherence_72</t>
+          <t>providedWithInformationOnFpAndDualContraception_72</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3392,17 +3310,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reason for fair or poor Cotrimoxazole Adherence</t>
+          <t>Client/partner use FP methods (other than condom):</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3417,7 +3335,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>reasonForFairOrPoorCotrimoxazoleAdherence_73</t>
+          <t>clientpartnerUseFpMethodsOtherThanCondom_73</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3433,17 +3351,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Reason for fair or poor Cotrimoxazole Adherence (2)</t>
+          <t>Correct condom use demonstrated</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3458,7 +3376,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>reasonForFairOrPoorCotrimoxazoleAdherence2_74</t>
+          <t>correctCondomUseDemonstrated_74</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3474,17 +3392,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>INH adherence</t>
+          <t>Client/partner use condoms as (one) FP method</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3499,7 +3417,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>inhAdherence_75</t>
+          <t>clientpartnerUseCondomsAsOneFpMethod_75</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -3515,17 +3433,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Reason for fair or poor INH Adherence</t>
+          <t>Condoms provided to client</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3540,7 +3458,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>reasonForFairOrPoorInhAdherence_76</t>
+          <t>condomsProvidedToClient_76</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -3556,17 +3474,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TPT Type</t>
+          <t>Client referred to other services</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3581,7 +3499,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>tptType_77</t>
+          <t>clientReferredToOtherServices_77</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -3597,17 +3515,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Post Test Counseling</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TPT Type (2)</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3622,7 +3540,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>tptType2_78</t>
+          <t>comments_78</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -3638,17 +3556,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TPT Type (3)</t>
+          <t>Consent given for index elicitation and contact</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3663,7 +3581,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>tptType3_79</t>
+          <t>consentGivenForIndexElicitationAndContact_79</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -3679,22 +3597,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3HP Weekly</t>
+          <t>Spouse full name</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3704,13 +3622,13 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>3hpWeekly_80</t>
+          <t>spouseFullName_80</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3720,17 +3638,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Medications out of stock</t>
+          <t>Partner Gender</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3745,7 +3663,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>medicationsOutOfStock_81</t>
+          <t>partnerGender_81</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -3761,17 +3679,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1HP Daily</t>
+          <t>Index type</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3786,7 +3704,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1hpDaily_82</t>
+          <t>indexType_82</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -3802,22 +3720,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>INH Dose</t>
+          <t>Index Descriptive Address</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3827,13 +3745,13 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>inhDose_83</t>
+          <t>indexDescriptiveAddress_83</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3843,17 +3761,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Prescribed Medications</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Other drugs prescribed</t>
+          <t>Index Relation Phone</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3868,7 +3786,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>otherDrugsPrescribed_84</t>
+          <t>indexRelationPhone_84</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3884,22 +3802,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TESTS ORDERED</t>
+          <t>Spouse full name (2)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3909,13 +3827,13 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>testsOrdered_85</t>
+          <t>spouseFullName2_85</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3925,17 +3843,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TESTS ORDERED (2)</t>
+          <t>Partner Gender (2)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3950,7 +3868,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>testsOrdered2_86</t>
+          <t>partnerGender2_86</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3966,17 +3884,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TESTS ORDERED (3)</t>
+          <t>Index type (2)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3991,7 +3909,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>testsOrdered3_87</t>
+          <t>indexType2_87</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -4007,22 +3925,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indication For The Viral Load Test</t>
+          <t>Index Descriptive Address (2)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4032,13 +3950,13 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>indicationForTheViralLoadTest_88</t>
+          <t>indexDescriptiveAddress2_88</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4048,25 +3966,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CD4
-Viral Load
-Esophageal Thrush
-                    Indication for Viral Load Test</t>
+          <t>Index Relation Phone (2)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4076,13 +3991,13 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>cd4viralLoadesophagealThrushIndicationForViralLoadTest_89</t>
+          <t>indexRelationPhone2_89</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -4092,25 +4007,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CD4
-Viral Load
-Esophageal Thrush
-                    Indication for Viral Load Test (2)</t>
+          <t>Spouse full name (3)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4120,13 +4032,13 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>cd4viralLoadesophagealThrushIndicationForViralLoadTest2_90</t>
+          <t>spouseFullName3_90</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4136,20 +4048,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CD4
-Viral Load
-Esophageal Thrush
-                    Indication for Viral Load Test (3)</t>
+          <t>Partner Gender (3)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4164,7 +4073,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>cd4viralLoadesophagealThrushIndicationForViralLoadTest3_91</t>
+          <t>partnerGender3_91</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -4180,20 +4089,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CD4
-Viral Load
-Esophageal Thrush
-                    Indication for Viral Load Test (4)</t>
+          <t>Index type (3)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4208,7 +4114,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>cd4viralLoadesophagealThrushIndicationForViralLoadTest4_92</t>
+          <t>indexType3_92</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4224,25 +4130,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CD4
-Viral Load
-Esophageal Thrush
-                    Indication for Viral Load Test (5)</t>
+          <t>Index Descriptive Address (3)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4252,13 +4155,13 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>cd4viralLoadesophagealThrushIndicationForViralLoadTest5_93</t>
+          <t>indexDescriptiveAddress3_93</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4268,26 +4171,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HB/PCV
-WBC + Diff
-ALT
-AST
-Differential Lymphocytes count (DLC)</t>
+          <t>Index Relation Phone (3)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4297,13 +4196,13 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>hbpcvwbcDiffaltastdifferentialLymphocytesCountDlc_94</t>
+          <t>indexRelationPhone3_94</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4313,26 +4212,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HB/PCV
-WBC + Diff
-ALT
-AST
-Differential Lymphocytes count (DLC) (2)</t>
+          <t>Spouse full name (4)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4342,13 +4237,13 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>hbpcvwbcDiffaltastdifferentialLymphocytesCountDlc2_95</t>
+          <t>spouseFullName4_95</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4358,21 +4253,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HB/PCV
-WBC + Diff
-ALT
-AST
-Differential Lymphocytes count (DLC) (3)</t>
+          <t>Partner Gender (4)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4387,7 +4278,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>hbpcvwbcDiffaltastdifferentialLymphocytesCountDlc3_96</t>
+          <t>partnerGender4_96</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -4403,21 +4294,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HB/PCV
-WBC + Diff
-ALT
-AST
-Differential Lymphocytes count (DLC) (4)</t>
+          <t>Index type (4)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4432,7 +4319,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>hbpcvwbcDiffaltastdifferentialLymphocytesCountDlc4_97</t>
+          <t>indexType4_97</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -4448,26 +4335,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HB/PCV
-WBC + Diff
-ALT
-AST
-Differential Lymphocytes count (DLC) (5)</t>
+          <t>Index Descriptive Address (4)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4477,13 +4360,13 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>hbpcvwbcDiffaltastdifferentialLymphocytesCountDlc5_98</t>
+          <t>indexDescriptiveAddress4_98</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -4493,26 +4376,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Creatinine
-Lipid Profile
-HBsAg
-HCV
-Total lymphocytes count (TLC)</t>
+          <t>Index Relation Phone (4)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4522,13 +4401,13 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>creatininelipidProfilehbsaghcvtotalLymphocytesCountTlc_99</t>
+          <t>indexRelationPhone4_99</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -4538,26 +4417,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Creatinine
-Lipid Profile
-HBsAg
-HCV
-Total lymphocytes count (TLC) (2)</t>
+          <t>Spouse full name (5)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4567,13 +4442,13 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>creatininelipidProfilehbsaghcvtotalLymphocytesCountTlc2_100</t>
+          <t>spouseFullName5_100</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4583,21 +4458,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Creatinine
-Lipid Profile
-HBsAg
-HCV
-Total lymphocytes count (TLC) (3)</t>
+          <t>Partner Gender (5)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4612,7 +4483,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>creatininelipidProfilehbsaghcvtotalLymphocytesCountTlc3_101</t>
+          <t>partnerGender5_101</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -4628,21 +4499,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Creatinine
-Lipid Profile
-HBsAg
-HCV
-Total lymphocytes count (TLC) (4)</t>
+          <t>Index type (5)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4657,7 +4524,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>creatininelipidProfilehbsaghcvtotalLymphocytesCountTlc4_102</t>
+          <t>indexType5_102</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -4673,21 +4540,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lab Plan</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Creatinine
-Lipid Profile
-HBsAg
-HCV
-Total lymphocytes count (TLC) (5)</t>
+          <t>Index Descriptive Address (5)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4702,7 +4565,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>creatininelipidProfilehbsaghcvtotalLymphocytesCountTlc5_103</t>
+          <t>indexDescriptiveAddress5_103</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -4718,22 +4581,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>REFERRALS ORDERED</t>
+          <t>Index Relation Phone (5)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4743,13 +4606,13 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>referralsOrdered_104</t>
+          <t>indexRelationPhone5_104</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -4759,22 +4622,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>REFERRALS ORDERED (2)</t>
+          <t>Spouse full name (6)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4784,13 +4647,13 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>referralsOrdered2_105</t>
+          <t>spouseFullName6_105</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -4800,17 +4663,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>REFERRALS ORDERED (3)</t>
+          <t>Partner Gender (6)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4825,7 +4688,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>referralsOrdered3_106</t>
+          <t>partnerGender6_106</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -4841,17 +4704,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>REFERRALS ORDERED (4)</t>
+          <t>Index type (6)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4866,7 +4729,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>referralsOrdered4_107</t>
+          <t>indexType6_107</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -4882,25 +4745,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Adherence Counseling
-Intensive Adherence Counseling
-Community Pharmacy
-Community ART</t>
+          <t>Index Descriptive Address (6)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4910,13 +4770,13 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>adherenceCounselingintensiveAdherenceCounselingcommunityPharmacycommunityArt_108</t>
+          <t>indexDescriptiveAddress6_108</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -4926,25 +4786,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Index Notification Services - Elicitation</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Adherence Counseling
-Intensive Adherence Counseling
-Community Pharmacy
-Community ART (2)</t>
+          <t>Index Relation Phone (6)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Coded</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4954,13 +4811,13 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>adherenceCounselingintensiveAdherenceCounselingcommunityPharmacycommunityArt2_109</t>
+          <t>indexRelationPhone6_109</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -4970,20 +4827,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>SYPHILIS TEST (VDRL)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Adherence Counseling
-Intensive Adherence Counseling
-Community Pharmacy
-Community ART (3)</t>
+          <t>Syphilis test result:</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4998,7 +4852,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>adherenceCounselingintensiveAdherenceCounselingcommunityPharmacycommunityArt3_110</t>
+          <t>syphilisTestResult_110</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -5014,20 +4868,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>SYPHILIS TEST (VDRL)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Adherence Counseling
-Intensive Adherence Counseling
-Community Pharmacy
-Community ART (4)</t>
+          <t>Hepatitis B virus test result:</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5042,7 +4893,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>adherenceCounselingintensiveAdherenceCounselingcommunityPharmacycommunityArt4_111</t>
+          <t>hepatitisBVirusTestResult_111</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -5058,25 +4909,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>SYPHILIS TEST (VDRL)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PMTCT Services
-STI Services
-TB Services
-OVC Program</t>
+          <t>Hepatitis C virus test result:</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5086,13 +4934,13 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>pmtctServicesstiServicestbServicesovcProgram_112</t>
+          <t>hepatitisCVirusTestResult_112</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5102,17 +4950,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Additional Comments/Clinical Notes</t>
+          <t>Population Type</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Additional Comments/Clinical Notes</t>
+          <t>Population Type</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Population Type</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5122,12 +4970,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>additionalComments_113</t>
+          <t>populationType_113</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -5143,22 +4991,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Appointment and Signatures</t>
+          <t>Population Type</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Appointment and Signatures</t>
+          <t>Population Type</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Next Appointment Date:</t>
+          <t>KP Type</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Coded</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5168,18 +5016,100 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>nextAppointmentDate_114</t>
+          <t>kpType_114</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Population Type</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Population Type</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>KP Type (2)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Coded</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>kpType2_115</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Signature and date</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Signature and date</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>date_116</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
